--- a/_906_ArmorsText.xlsx
+++ b/_906_ArmorsText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C172ED-9680-4DDF-81E8-2AE2B9C1D5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D7DFB7-4C03-45CA-8598-693C639103AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,54 +62,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp Card</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>経験値カード</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 카드</t>
-  </si>
-  <si>
-    <t>ゴールド</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>크리스탈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crystal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>クリスタル</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>희귀한 마력이 응축된 신비한 결정체.
-캐릭터 소환과 각종 특별 상품 구매에 사용된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A mysterious crystal condensed with rare magical energy.
-Used to summon characters and purchase various special items.</t>
+    <t>평범한 셔츠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain Shirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通のシャツ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별한 특징이 없는 평범한 셔츠입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An ordinary shirt with no special features.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>希少な魔力が凝縮された神秘的な結晶。
-キャラクタ</t>
+      <t>特別な特</t>
     </r>
     <r>
       <rPr>
@@ -119,21 +93,33 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>ーの募集や、さまざまな特別商品との交換に使用できる。</t>
+      <t>徴のない普通のシャツです。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>플레이어 경험치 카드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player Exp Card</t>
+    <t>평범한 바지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain Pants</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通のズボン</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별한 특징이 없는 평범한 바지입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ordinary pants with no special features.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>プレイヤ</t>
+      <t>特別な特</t>
     </r>
     <r>
       <rPr>
@@ -143,23 +129,33 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>ー経験値カード</t>
+      <t>徴のない普通のズボンです。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>플레이어의 성장을 돕는 경험치가 담긴 카드.
-획득 시 플레이어 경험치를 얻는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A card containing experience to aid the player’s growth.
-Grants Player EXP when obtained.</t>
+    <t>평범한 장갑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain Gloves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通の手袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별한 특징이 없는 평범한 장갑입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ordinary gloves with no special features.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>プレイヤ</t>
+      <t>特別な特</t>
     </r>
     <r>
       <rPr>
@@ -169,19 +165,81 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>ーの成長を助ける経験値が込められたカード。</t>
+      <t>徴のない普通の手袋です。</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 신발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 장갑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 신발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fine Shoes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上質な靴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋은 소재로 제작되어 착용감과 내구성이 향상된 신발입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shoes made from quality materials for improved comfort and durability.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上質な素材で作られ、履き心地と耐久性に優れた靴です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fine Gloves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上質な手袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋은 소재로 제작되어 착용감과 내구성이 향상된 장갑입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloves made from quality materials for improved comfort and durability.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上質な素材で作られ、着け心地と耐久性に優れた手袋です。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain Shoes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通の靴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별한 특징이 없는 평범한 신발입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ordinary shoes with no special features.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-獲得時にプレイヤ</t>
+      <t>特別な特</t>
     </r>
     <r>
       <rPr>
@@ -191,103 +249,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>ー経験値を獲得する。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터와 무기의 성장을 돕는 경험치가 담긴 카드.
-사용 시 선택한 캐릭터 또는 무기의 경험치를 증가시킨다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>キャラクタ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーと武器の成長を助ける経験値が込められたカード。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-使用すると選</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>択したキャラクターまたは武器の経験値が増加する。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A card containing experience to aid the growth of characters and weapons.
-Use it to grant EXP to the selected character or weapon.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 내에서 널리 사용되는 일반 재화.
-캐릭터와 무기의 성장 및 각종 상품 구매에 사용된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A common currency widely used throughout the game.
-Used to upgrade characters and weapons and purchase various items.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ゲ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーム内で広く使用される一般的な通貨。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-キャラクタ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーや武器の強化、さまざまな商品の購入に使用される。</t>
+      <t>徴のない普通の靴です。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -714,14 +676,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
   <dimension ref="A2:D54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="11" width="18.640625" customWidth="1"/>
-    <col min="12" max="34" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5625" customWidth="1"/>
+    <col min="2" max="11" width="18.625" customWidth="1"/>
+    <col min="12" max="34" width="12.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -749,65 +711,65 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
-        <v>9040001</v>
+        <v>9060001</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="35.25" x14ac:dyDescent="0.6">
+      <c r="A5" s="3">
+        <v>9060002</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A6" s="2">
+        <v>9060003</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="123" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3">
-        <v>9040002</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="35.25" x14ac:dyDescent="0.6">
+      <c r="A7" s="3">
+        <v>9060004</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" ht="18.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2">
-        <v>9040003</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3">
-        <v>9040004</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" ht="18.45" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
-        <v>9040005</v>
+        <v>9060005</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -819,9 +781,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="92.15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="35.25" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
-        <v>9040006</v>
+        <v>9060006</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>21</v>
@@ -833,77 +795,129 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" ht="18.45" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
       <c r="A10" s="2">
-        <v>9040007</v>
+        <v>9060007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="147.44999999999999" x14ac:dyDescent="0.55000000000000004">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="35.25" x14ac:dyDescent="0.6">
       <c r="A11" s="3">
-        <v>9040008</v>
+        <v>9060008</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="2">
+        <v>9060009</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="3">
+        <v>9060010</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="2">
+        <v>9060011</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="3">
+        <v>9060012</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
